--- a/tests/yuhi/profile.xlsx
+++ b/tests/yuhi/profile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1221e7247ec036c5/^F^F^F2025 Yuhi/Model Code/PATMO input files/yuhi input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1221e7247ec036c5/PATMO/PATMO-yuhi/tests/yuhi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="266" documentId="8_{6B81276A-83FB-A843-A3BB-2D87888D32D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4FE470B-97D8-42E8-85A5-55C10220E054}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="8_{6B81276A-83FB-A843-A3BB-2D87888D32D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0FA10F7-FDD6-4B67-ABE4-5D9928BDC788}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="0" windowWidth="28290" windowHeight="18975" xr2:uid="{D7BD78CA-9E1A-A84E-ABC8-B9A18946ED57}"/>
+    <workbookView xWindow="3060" yWindow="3120" windowWidth="19140" windowHeight="16995" xr2:uid="{D7BD78CA-9E1A-A84E-ABC8-B9A18946ED57}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -1143,7 +1143,7 @@
         <v>902.21929</v>
       </c>
       <c r="D2" s="1">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E2">
         <v>282</v>
@@ -1452,7 +1452,7 @@
         <v>797.63786000000005</v>
       </c>
       <c r="D3" s="1">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E3">
         <v>275</v>
@@ -1761,7 +1761,7 @@
         <v>703.47653000000003</v>
       </c>
       <c r="D4" s="1">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E4">
         <v>269</v>
@@ -2070,7 +2070,7 @@
         <v>618.19354999999996</v>
       </c>
       <c r="D5" s="1">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E5">
         <v>262</v>
@@ -2379,7 +2379,7 @@
         <v>541.80885999999998</v>
       </c>
       <c r="D6" s="1">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E6">
         <v>256</v>
@@ -2688,7 +2688,7 @@
         <v>472.96440000000001</v>
       </c>
       <c r="D7" s="1">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E7">
         <v>249</v>
@@ -2997,7 +2997,7 @@
         <v>411.18493000000001</v>
       </c>
       <c r="D8" s="1">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E8">
         <v>243</v>
@@ -3306,7 +3306,7 @@
         <v>356.01877999999999</v>
       </c>
       <c r="D9" s="1">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E9">
         <v>236</v>
@@ -3615,7 +3615,7 @@
         <v>305.89278999999999</v>
       </c>
       <c r="D10" s="1">
-        <v>89400</v>
+        <v>178800</v>
       </c>
       <c r="E10">
         <v>230</v>
@@ -3924,7 +3924,7 @@
         <v>260.87290999999999</v>
       </c>
       <c r="D11" s="1">
-        <v>49000</v>
+        <v>98000</v>
       </c>
       <c r="E11">
         <v>225</v>
@@ -4233,7 +4233,7 @@
         <v>222.53259</v>
       </c>
       <c r="D12" s="1">
-        <v>22600</v>
+        <v>45200</v>
       </c>
       <c r="E12">
         <v>221</v>
@@ -4542,7 +4542,7 @@
         <v>190.59133</v>
       </c>
       <c r="D13" s="1">
-        <v>11700</v>
+        <v>23400</v>
       </c>
       <c r="E13">
         <v>220</v>
@@ -4851,7 +4851,7 @@
         <v>161.12042</v>
       </c>
       <c r="D14" s="1">
-        <v>6810</v>
+        <v>13620</v>
       </c>
       <c r="E14">
         <v>219</v>
@@ -5160,7 +5160,7 @@
         <v>136.30518000000001</v>
       </c>
       <c r="D15" s="1">
-        <v>5170</v>
+        <v>10340</v>
       </c>
       <c r="E15">
         <v>218</v>
@@ -5469,7 +5469,7 @@
         <v>115.65243</v>
       </c>
       <c r="D16" s="1">
-        <v>4290</v>
+        <v>8580</v>
       </c>
       <c r="E16">
         <v>217</v>
@@ -5778,7 +5778,7 @@
         <v>98.663640000000001</v>
       </c>
       <c r="D17" s="1">
-        <v>3950</v>
+        <v>7900</v>
       </c>
       <c r="E17">
         <v>217</v>
@@ -6087,7 +6087,7 @@
         <v>84.091210000000004</v>
       </c>
       <c r="D18" s="1">
-        <v>3900</v>
+        <v>7800</v>
       </c>
       <c r="E18">
         <v>217</v>
@@ -6396,7 +6396,7 @@
         <v>71.197580000000002</v>
       </c>
       <c r="D19" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="E19">
         <v>217</v>
@@ -6705,7 +6705,7 @@
         <v>60.297530000000002</v>
       </c>
       <c r="D20" s="1">
-        <v>4340</v>
+        <v>8680</v>
       </c>
       <c r="E20">
         <v>217</v>
@@ -7014,7 +7014,7 @@
         <v>51.357950000000002</v>
       </c>
       <c r="D21" s="1">
-        <v>4840</v>
+        <v>9680</v>
       </c>
       <c r="E21">
         <v>217</v>
@@ -7323,7 +7323,7 @@
         <v>43.980049999999999</v>
       </c>
       <c r="D22" s="1">
-        <v>5440</v>
+        <v>10880</v>
       </c>
       <c r="E22">
         <v>218</v>
@@ -7632,7 +7632,7 @@
         <v>37.324809999999999</v>
       </c>
       <c r="D23" s="1">
-        <v>6190</v>
+        <v>12380</v>
       </c>
       <c r="E23">
         <v>219</v>
@@ -7941,7 +7941,7 @@
         <v>31.690169999999998</v>
       </c>
       <c r="D24" s="1">
-        <v>7040</v>
+        <v>14080</v>
       </c>
       <c r="E24">
         <v>220</v>
@@ -8250,7 +8250,7 @@
         <v>26.926629999999999</v>
       </c>
       <c r="D25" s="1">
-        <v>7980</v>
+        <v>15960</v>
       </c>
       <c r="E25">
         <v>221</v>
@@ -8559,7 +8559,7 @@
         <v>23.049440000000001</v>
       </c>
       <c r="D26" s="1">
-        <v>8990</v>
+        <v>17980</v>
       </c>
       <c r="E26">
         <v>222</v>
@@ -8868,7 +8868,7 @@
         <v>19.810359999999999</v>
       </c>
       <c r="D27" s="1">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E27">
         <v>223</v>
@@ -9177,7 +9177,7 @@
         <v>16.90692</v>
       </c>
       <c r="D28" s="1">
-        <v>11300</v>
+        <v>22600</v>
       </c>
       <c r="E28">
         <v>224</v>
@@ -9486,7 +9486,7 @@
         <v>14.45824</v>
       </c>
       <c r="D29" s="1">
-        <v>12500</v>
+        <v>25000</v>
       </c>
       <c r="E29">
         <v>225</v>
@@ -9795,7 +9795,7 @@
         <v>12.39631</v>
       </c>
       <c r="D30" s="1">
-        <v>13600</v>
+        <v>27200</v>
       </c>
       <c r="E30">
         <v>226</v>
@@ -10104,7 +10104,7 @@
         <v>10.759230000000001</v>
       </c>
       <c r="D31" s="1">
-        <v>15100</v>
+        <v>30200</v>
       </c>
       <c r="E31">
         <v>227</v>
@@ -10413,7 +10413,7 @@
         <v>9.2407000000000004</v>
       </c>
       <c r="D32" s="1">
-        <v>16700</v>
+        <v>33400</v>
       </c>
       <c r="E32">
         <v>229</v>
@@ -10722,7 +10722,7 @@
         <v>7.9389900000000004</v>
       </c>
       <c r="D33" s="1">
-        <v>18200</v>
+        <v>36400</v>
       </c>
       <c r="E33">
         <v>231</v>
@@ -11031,7 +11031,7 @@
         <v>6.8358800000000004</v>
       </c>
       <c r="D34" s="1">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E34">
         <v>233</v>
@@ -11340,7 +11340,7 @@
         <v>5.9101400000000002</v>
       </c>
       <c r="D35" s="1">
-        <v>22000</v>
+        <v>44000</v>
       </c>
       <c r="E35">
         <v>235</v>
@@ -11649,7 +11649,7 @@
         <v>5.1526699999999996</v>
       </c>
       <c r="D36" s="1">
-        <v>24500</v>
+        <v>49000</v>
       </c>
       <c r="E36">
         <v>237</v>
@@ -11958,7 +11958,7 @@
         <v>4.4457700000000004</v>
       </c>
       <c r="D37" s="1">
-        <v>27500</v>
+        <v>55000</v>
       </c>
       <c r="E37">
         <v>239</v>
@@ -12267,7 +12267,7 @@
         <v>3.8460100000000002</v>
       </c>
       <c r="D38" s="1">
-        <v>30500</v>
+        <v>61000</v>
       </c>
       <c r="E38">
         <v>242</v>
@@ -12576,7 +12576,7 @@
         <v>3.34199</v>
       </c>
       <c r="D39" s="1">
-        <v>33900</v>
+        <v>67800</v>
       </c>
       <c r="E39">
         <v>245</v>
@@ -12885,7 +12885,7 @@
         <v>2.92517</v>
       </c>
       <c r="D40" s="1">
-        <v>38000</v>
+        <v>76000</v>
       </c>
       <c r="E40">
         <v>248</v>
@@ -13194,7 +13194,7 @@
         <v>2.54569</v>
       </c>
       <c r="D41" s="1">
-        <v>42000</v>
+        <v>84000</v>
       </c>
       <c r="E41">
         <v>250</v>
@@ -13503,7 +13503,7 @@
         <v>2.20919</v>
       </c>
       <c r="D42" s="1">
-        <v>46400</v>
+        <v>92800</v>
       </c>
       <c r="E42">
         <v>253</v>
@@ -13812,7 +13812,7 @@
         <v>1.92266</v>
       </c>
       <c r="D43" s="1">
-        <v>51900</v>
+        <v>103800</v>
       </c>
       <c r="E43">
         <v>256</v>
@@ -14121,7 +14121,7 @@
         <v>1.67906</v>
       </c>
       <c r="D44" s="1">
-        <v>58400</v>
+        <v>116800</v>
       </c>
       <c r="E44">
         <v>259</v>
@@ -14430,7 +14430,7 @@
         <v>1.4777800000000001</v>
       </c>
       <c r="D45" s="1">
-        <v>64500</v>
+        <v>129000</v>
       </c>
       <c r="E45">
         <v>261</v>
@@ -14739,7 +14739,7 @@
         <v>1.2892399999999999</v>
       </c>
       <c r="D46" s="1">
-        <v>71400</v>
+        <v>142800</v>
       </c>
       <c r="E46">
         <v>264</v>
@@ -15048,7 +15048,7 @@
         <v>1.1295200000000001</v>
       </c>
       <c r="D47" s="1">
-        <v>79900</v>
+        <v>159800</v>
       </c>
       <c r="E47">
         <v>267</v>
@@ -15357,7 +15357,7 @@
         <v>0.99112999999999996</v>
       </c>
       <c r="D48" s="1">
-        <v>87900</v>
+        <v>175800</v>
       </c>
       <c r="E48">
         <v>268</v>
@@ -15666,7 +15666,7 @@
         <v>0.87309000000000003</v>
       </c>
       <c r="D49" s="1">
-        <v>96900</v>
+        <v>193800</v>
       </c>
       <c r="E49">
         <v>269</v>
@@ -15975,7 +15975,7 @@
         <v>0.76271999999999995</v>
       </c>
       <c r="D50" s="1">
-        <v>107000</v>
+        <v>214000</v>
       </c>
       <c r="E50">
         <v>271</v>
@@ -16284,7 +16284,7 @@
         <v>0.66534000000000004</v>
       </c>
       <c r="D51" s="1">
-        <v>118000</v>
+        <v>236000</v>
       </c>
       <c r="E51">
         <v>271</v>
@@ -16593,7 +16593,7 @@
         <v>0.58026999999999995</v>
       </c>
       <c r="D52" s="1">
-        <v>132000</v>
+        <v>264000</v>
       </c>
       <c r="E52">
         <v>271</v>
@@ -16902,7 +16902,7 @@
         <v>0.50612000000000001</v>
       </c>
       <c r="D53" s="1">
-        <v>148000</v>
+        <v>296000</v>
       </c>
       <c r="E53">
         <v>268</v>
@@ -17211,7 +17211,7 @@
         <v>0.44535999999999998</v>
       </c>
       <c r="D54" s="1">
-        <v>166000</v>
+        <v>332000</v>
       </c>
       <c r="E54">
         <v>266</v>
@@ -17520,7 +17520,7 @@
         <v>0.38612000000000002</v>
       </c>
       <c r="D55" s="1">
-        <v>183000</v>
+        <v>366000</v>
       </c>
       <c r="E55">
         <v>264</v>
@@ -17829,7 +17829,7 @@
         <v>0.3347</v>
       </c>
       <c r="D56" s="1">
-        <v>202000</v>
+        <v>404000</v>
       </c>
       <c r="E56">
         <v>261</v>
@@ -18138,7 +18138,7 @@
         <v>0.28953000000000001</v>
       </c>
       <c r="D57" s="1">
-        <v>226000</v>
+        <v>452000</v>
       </c>
       <c r="E57">
         <v>259</v>
@@ -18447,7 +18447,7 @@
         <v>0.24976999999999999</v>
       </c>
       <c r="D58" s="1">
-        <v>252000</v>
+        <v>504000</v>
       </c>
       <c r="E58">
         <v>256</v>
@@ -18756,7 +18756,7 @@
         <v>0.21759000000000001</v>
       </c>
       <c r="D59" s="1">
-        <v>277000</v>
+        <v>554000</v>
       </c>
       <c r="E59">
         <v>254</v>
@@ -19065,7 +19065,7 @@
         <v>0.18723000000000001</v>
       </c>
       <c r="D60" s="1">
-        <v>307000</v>
+        <v>614000</v>
       </c>
       <c r="E60">
         <v>252</v>
@@ -19374,7 +19374,7 @@
         <v>0.15995999999999999</v>
       </c>
       <c r="D61" s="1">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="E61">
         <v>247</v>
